--- a/results/job_matches_2026-04-06.xlsx
+++ b/results/job_matches_2026-04-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=863b993691d43dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=f1696f58952c74ca</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer III – Big Data &amp; Analytics</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0657089c3ac9f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=863b993691d43dcd</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Python Engineer, Senior Associate</t>
+          <t>Software Engineer III – Big Data &amp; Analytics</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1ed8d52cd0705a</t>
+          <t>https://www.indeed.com/viewjob?jk=c0657089c3ac9f1d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer – Node.js &amp; Microservices</t>
+          <t>Python Engineer, Senior Associate</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>axiusSoftware</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,40 +636,75 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8416ad2ad931971c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1ed8d52cd0705a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>Senior Backend Engineer – Node.js &amp; Microservices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>axiusSoftware</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8416ad2ad931971c</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Data Analytics Engineer</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Salt Dental Partners</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Franklin, TN, US USA</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D8" t="n">
         <v>10.4</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>2026-04-05</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
         </is>

--- a/results/job_matches_2026-04-06.xlsx
+++ b/results/job_matches_2026-04-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -710,6 +710,111 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/job_matches_2026-04-06.xlsx
+++ b/results/job_matches_2026-04-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Deployment Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Gi Group</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Manor, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf73fd986d212e6</t>
+          <t>https://www.indeed.com/viewjob?jk=0f076f71ac1c6a4b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1696f58952c74ca</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf73fd986d212e6</t>
         </is>
       </c>
     </row>
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=863b993691d43dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=f1696f58952c74ca</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer III – Big Data &amp; Analytics</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0657089c3ac9f1d</t>
+          <t>https://www.indeed.com/viewjob?jk=863b993691d43dcd</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python Engineer, Senior Associate</t>
+          <t>Senior Backend Engineer – Node.js &amp; Microservices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>axiusSoftware</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1ed8d52cd0705a</t>
+          <t>https://www.indeed.com/viewjob?jk=8416ad2ad931971c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer – Node.js &amp; Microservices</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>axiusSoftware</t>
+          <t>Salt Dental Partners</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8416ad2ad931971c</t>
+          <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Salt Dental Partners</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,17 +696,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
+          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
+          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
+          <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Product Architect Google Cloud Platform</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Reston Hospital Center - Reston</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,52 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
+          <t>https://www.indeed.com/viewjob?jk=9800f97130992c45</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Product Architect Google Cloud Platform</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Catholic Medical Center</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Manchester, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1dfe8d6c036c24b4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-06.xlsx
+++ b/results/job_matches_2026-04-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Deployment Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Gi Group</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Manor, TX, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f076f71ac1c6a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf73fd986d212e6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf73fd986d212e6</t>
+          <t>https://www.indeed.com/viewjob?jk=f1696f58952c74ca</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Salt Dental Partners</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,94 +566,94 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1696f58952c74ca</t>
+          <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=863b993691d43dcd</t>
+          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer – Node.js &amp; Microservices</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>axiusSoftware</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8416ad2ad931971c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Salt Dental Partners</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,192 +661,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Product Architect Google Cloud Platform</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Reston Hospital Center - Reston</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Reston, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-05</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9800f97130992c45</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Product Architect Google Cloud Platform</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Catholic Medical Center</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Manchester, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Lambda, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Docker</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-05</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1dfe8d6c036c24b4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-06.xlsx
+++ b/results/job_matches_2026-04-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>UI/UX Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NIKSUN, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
+          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
         </is>
       </c>
     </row>
@@ -653,7 +653,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -671,7 +671,77 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Data Analyst (Sales Ops)- Temp</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hive, MapReduce, HBase, Scala, Oracle, SQL Server, ETL, Tableau</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45b583a24b7d9b26</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-06.xlsx
+++ b/results/job_matches_2026-04-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Qbtech</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf73fd986d212e6</t>
+          <t>https://www.indeed.com/viewjob?jk=d3c14d180cd784ef</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,94 +531,94 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1696f58952c74ca</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf73fd986d212e6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Genesys Cloud GenAI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Salt Dental Partners</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
+          <t>https://www.indeed.com/viewjob?jk=4735299b123e3950</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>UI/UX Engineer</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f1696f58952c74ca</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>AliCloud Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Vaarida Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
+          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Salt Dental Partners</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
+          <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>UI/UX Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NIKSUN, Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
+          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Analyst (Sales Ops)- Temp</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, MapReduce, HBase, Scala, Oracle, SQL Server, ETL, Tableau</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,77 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b583a24b7d9b26</t>
+          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-06.xlsx
+++ b/results/job_matches_2026-04-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,157 +468,157 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Qbtech</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Hadoop, HDFS, Hive, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3c14d180cd784ef</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf73fd986d212e6</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Genesys Cloud GenAI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf73fd986d212e6</t>
+          <t>https://www.indeed.com/viewjob?jk=4735299b123e3950</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Genesys Cloud GenAI Engineer</t>
+          <t>Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4735299b123e3950</t>
+          <t>https://www.indeed.com/viewjob?jk=f1696f58952c74ca</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>AliCloud Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Vaarida Technologies</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1696f58952c74ca</t>
+          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AliCloud Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vaarida Technologies</t>
+          <t>Salt Dental Partners</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,34 +626,34 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
+          <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>UI/UX Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Salt Dental Partners</t>
+          <t>NIKSUN, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,34 +661,34 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
+          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>UI/UX Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
+          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
+          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -775,41 +775,6 @@
         </is>
       </c>
       <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
         </is>

--- a/results/job_matches_2026-04-06.xlsx
+++ b/results/job_matches_2026-04-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Python Developer with AWS-2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>12.5</v>
+        <v>17.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf73fd986d212e6</t>
+          <t>https://www.indeed.com/viewjob?jk=3ee773ea630e1307</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Genesys Cloud GenAI Engineer</t>
+          <t>Senior MLOps Engineer - Analytics &amp; AI - R&amp;D - Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.8</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, Athena, RDS, Azure, GCP, Spark, Scala, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4735299b123e3950</t>
+          <t>https://www.indeed.com/viewjob?jk=b90e39d495953c19</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1696f58952c74ca</t>
+          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AliCloud Engineer</t>
+          <t>Data Engineer-4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vaarida Technologies</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
+          <t>https://www.indeed.com/viewjob?jk=238b37485205d9b2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Salt Dental Partners</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf73fd986d212e6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>UI/UX Engineer</t>
+          <t>Senior Databricks Administrator (AWS) New</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>Advanced software systems</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
+          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Genesys Cloud GenAI Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
+          <t>https://www.indeed.com/viewjob?jk=4735299b123e3950</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Healthfirst (New York)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,42 +741,392 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Software Engineer II, Data Platform</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f1696f58952c74ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AliCloud Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Vaarida Technologies</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Cupertino, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Salt Dental Partners</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Franklin, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Devops Engineer-1</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>UI/UX Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NIKSUN, Inc.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Senior Engineer</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>GEICO</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>Seattle, WA, US USA</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D18" t="n">
         <v>10.4</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ML Engineer / AI Operations-3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Morristown, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=757de7bfe898f867</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Data Analyst (Sales Ops)- Temp</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hive, MapReduce, HBase, Scala, Oracle, SQL Server, ETL, Tableau</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45b583a24b7d9b26</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-06.xlsx
+++ b/results/job_matches_2026-04-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer - Analytics &amp; AI - R&amp;D - Engineering</t>
+          <t>Software Engineering Advisor –Evernorth</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, GCP, Spark, Scala, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90e39d495953c19</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e200e992325ba5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Senior MLOps Engineer - Analytics &amp; AI - R&amp;D - Engineering</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Athena, RDS, Azure, GCP, Spark, Scala, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
+          <t>https://www.indeed.com/viewjob?jk=b90e39d495953c19</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer-4</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=238b37485205d9b2</t>
+          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer-4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf73fd986d212e6</t>
+          <t>https://www.indeed.com/viewjob?jk=238b37485205d9b2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Databricks Administrator (AWS) New</t>
+          <t>LLM Operations Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Advanced software systems</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
+          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Genesys Cloud GenAI Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4735299b123e3950</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf73fd986d212e6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Databricks Administrator (AWS) New</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Healthfirst (New York)</t>
+          <t>Advanced software systems</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
+          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Platform</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Healthfirst (New York)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,17 +766,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1696f58952c74ca</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
         </is>
       </c>
     </row>
@@ -888,7 +888,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Devops Engineer-1</t>
+          <t>Resiliency &amp; Recovery Engineer-1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
+          <t>https://www.indeed.com/viewjob?jk=7c68a7783ebf554b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>UI/UX Engineer</t>
+          <t>Devops Engineer-1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>ML Engineer / AI Operations-3</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
+          <t>https://www.indeed.com/viewjob?jk=757de7bfe898f867</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>UI/UX Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NIKSUN, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
+          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
+          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations-3</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757de7bfe898f867</t>
+          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Analyst (Sales Ops)- Temp</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, MapReduce, HBase, Scala, Oracle, SQL Server, ETL, Tableau</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,42 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b583a24b7d9b26</t>
+          <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Workday Consultant</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tardus inc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>AWS, Azure, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes, Jenkins, Git, Python</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=404fb8b0e1fceb3e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-06.xlsx
+++ b/results/job_matches_2026-04-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Python Developer with AWS-2</t>
+          <t>DataOps Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.4</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, GCP, Hadoop, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, S3, IAM, RDS, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee773ea630e1307</t>
+          <t>https://www.indeed.com/viewjob?jk=31364c52fe931267</t>
         </is>
       </c>
     </row>
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
+          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer-4</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Google Cloud Platform, GCP, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=238b37485205d9b2</t>
+          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LLM Operations Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>GAINSCO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
+          <t>https://www.indeed.com/viewjob?jk=322e0a73c296fcdc</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>IT System Administrator</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t xml:space="preserve">Tailored Edge Connections </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>North Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf73fd986d212e6</t>
+          <t>https://www.indeed.com/viewjob?jk=f856c765cc7cbf0f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Databricks Administrator (AWS) New</t>
+          <t>LLM Operations Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Advanced software systems</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
+          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
         </is>
       </c>
     </row>
@@ -753,55 +753,55 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Healthfirst (New York)</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf73fd986d212e6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
+          <t>Senior Databricks Administrator (AWS) New</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Advanced software systems</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
+          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AliCloud Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vaarida Technologies</t>
+          <t>Healthfirst (New York)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,49 +846,49 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Salt Dental Partners</t>
+          <t>Qorvo</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
+          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Resiliency &amp; Recovery Engineer-1</t>
+          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -898,15 +898,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, SQL Server, Splunk, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c68a7783ebf554b</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Devops Engineer-1</t>
+          <t>Software Engineer II - Identity &amp; Access Management</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, IAM, RDS, Kafka, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
+          <t>https://www.indeed.com/viewjob?jk=2429610d97c33cfd</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ML Engineer / AI Operations-3</t>
+          <t>AliCloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Vaarida Technologies</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Scala, Kafka, Snowflake, Data Modeling, ELT, Power BI, MLflow, CI/CD</t>
+          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=757de7bfe898f867</t>
+          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UI/UX Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>Salt Dental Partners</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
+          <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Devops Engineer-1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
+          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>UI/UX Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NIKSUN, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
+          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
+          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Workday Consultant</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tardus inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,15 +1151,85 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Workday Consultant</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tardus inc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>AWS, Azure, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes, Jenkins, Git, Python</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=404fb8b0e1fceb3e</t>
         </is>

--- a/results/job_matches_2026-04-06.xlsx
+++ b/results/job_matches_2026-04-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior VR/XR &amp; Computer Vision Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Qorvo</t>
+          <t>IVN</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, Scala, PostgreSQL, MySQL, NoSQL, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe26087c7f2c3c7</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
+          <t>Sr Java Application Developer **REMOTE AVAILABLE**</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Vanderbilt University Medical Center</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>EMR, RDS, Azure, Databricks, GCP, Scala, MySQL, MS Excel, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
+          <t>https://www.indeed.com/viewjob?jk=37699040bc322434</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer II - Identity &amp; Access Management</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Qorvo</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Kafka, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2429610d97c33cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AliCloud Engineer</t>
+          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vaarida Technologies</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Software Engineer II - Identity &amp; Access Management</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Salt Dental Partners</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, API Gateway, IAM, RDS, Kafka, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
+          <t>https://www.indeed.com/viewjob?jk=2429610d97c33cfd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Devops Engineer-1</t>
+          <t>AliCloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Vaarida Technologies</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
+          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>UI/UX Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>Salt Dental Partners</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
+          <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Devops Engineer-1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
+          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Workday Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tardus inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
+          <t>https://www.indeed.com/viewjob?jk=404fb8b0e1fceb3e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>UI/UX Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NIKSUN, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
+          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Workday Consultant</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tardus inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes, Jenkins, Git, Python</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,77 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=404fb8b0e1fceb3e</t>
+          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-06.xlsx
+++ b/results/job_matches_2026-04-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor –Evernorth</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>oura</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse</t>
+          <t>AWS, Glue, Kinesis, Athena, S3, RDS, Azure, Databricks, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e200e992325ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=42ae77d7fc82e8f5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer - Analytics &amp; AI - R&amp;D - Engineering</t>
+          <t>Software Engineering Advisor –Evernorth</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, GCP, Spark, Scala, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90e39d495953c19</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e200e992325ba5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior MLOps Engineer - Analytics &amp; AI - R&amp;D - Engineering</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Athena, RDS, Azure, GCP, Spark, Scala, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
+          <t>https://www.indeed.com/viewjob?jk=b90e39d495953c19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
+          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GAINSCO</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=322e0a73c296fcdc</t>
+          <t>https://www.indeed.com/viewjob?jk=e41b246b13bc8e16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>IT System Administrator</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tailored Edge Connections </t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>North Aurora, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f856c765cc7cbf0f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d05ebd191671b98</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LLM Operations Engineer</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
+          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>GAINSCO</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf73fd986d212e6</t>
+          <t>https://www.indeed.com/viewjob?jk=322e0a73c296fcdc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Databricks Administrator (AWS) New</t>
+          <t>IT System Administrator</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Advanced software systems</t>
+          <t xml:space="preserve">Tailored Edge Connections </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>North Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,19 +811,19 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
+          <t>https://www.indeed.com/viewjob?jk=f856c765cc7cbf0f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>LLM Operations Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Healthfirst (New York)</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
+          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior VR/XR &amp; Computer Vision Software Engineer</t>
+          <t>Senior IT Database Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>IVN</t>
+          <t>Pegasystems</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, PostgreSQL, MySQL, NoSQL, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe26087c7f2c3c7</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Java Application Developer **REMOTE AVAILABLE**</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Vanderbilt University Medical Center</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Databricks, GCP, Scala, MySQL, MS Excel, CI/CD, Docker</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37699040bc322434</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf73fd986d212e6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Qorvo</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=998975ecfa0fdb90</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Clarks Summit, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II - Identity &amp; Access Management</t>
+          <t>Senior Databricks Administrator (AWS) New</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Advanced software systems</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Kafka, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2429610d97c33cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AliCloud Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vaarida Technologies</t>
+          <t>Healthfirst (New York)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Salt Dental Partners</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Devops Engineer-1</t>
+          <t>Senior VR/XR &amp; Computer Vision Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>IVN</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Scala, PostgreSQL, MySQL, NoSQL, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe26087c7f2c3c7</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Workday Consultant</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tardus inc</t>
+          <t>Qorvo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, PostgreSQL, MySQL, CI/CD, Jenkins, Kubernetes, Jenkins, Git, Python</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=404fb8b0e1fceb3e</t>
+          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>UI/UX Engineer</t>
+          <t>Sr Java Application Developer **REMOTE AVAILABLE**</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>Vanderbilt University Medical Center</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
+          <t>EMR, RDS, Azure, Databricks, GCP, Scala, MySQL, MS Excel, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
+          <t>https://www.indeed.com/viewjob?jk=37699040bc322434</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Software Engineer II - Identity &amp; Access Management</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, API Gateway, IAM, RDS, Kafka, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
+          <t>https://www.indeed.com/viewjob?jk=2429610d97c33cfd</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>AliCloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Vaarida Technologies</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,17 +1291,297 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
+          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Salt Dental Partners</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Franklin, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Devops Engineer-1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>UI/UX Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>NIKSUN, Inc.</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Data Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Trenton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81fc0c21d444af23</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-06.xlsx
+++ b/results/job_matches_2026-04-06.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,25 +538,25 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor –Evernorth</t>
+          <t>Intern - Data Engineer - Summer 2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>Acxiom</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>Conway, AR, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse</t>
+          <t>AWS, S3, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e200e992325ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=338baa6df1016586</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer - Analytics &amp; AI - R&amp;D - Engineering</t>
+          <t>Software Engineering Advisor –Evernorth</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>The Cigna Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bloomington, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, GCP, Spark, Scala, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90e39d495953c19</t>
+          <t>https://www.indeed.com/viewjob?jk=d6e200e992325ba5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior MLOps Engineer - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Athena, RDS, Azure, GCP, Spark, Scala, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
+          <t>https://www.indeed.com/viewjob?jk=b90e39d495953c19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41b246b13bc8e16</t>
+          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d05ebd191671b98</t>
+          <t>https://www.indeed.com/viewjob?jk=e41b246b13bc8e16</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d05ebd191671b98</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GAINSCO</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=322e0a73c296fcdc</t>
+          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>IT System Administrator</t>
+          <t>Software Engineer III - Full Stack + AWS + Elastic / Open Search</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tailored Edge Connections </t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>North Aurora, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, EMR, S3, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, MLOps</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f856c765cc7cbf0f</t>
+          <t>https://www.indeed.com/viewjob?jk=0ce76eb1050277d8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LLM Operations Engineer</t>
+          <t>Healthcare Application Developer (AWS / Clinical AI)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>Careficient</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, SQS, SNS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
+          <t>https://www.indeed.com/viewjob?jk=76e0e8781165273c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior IT Database Engineer</t>
+          <t>LLM Operations Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Pegasystems</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
+          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>GAINSCO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf73fd986d212e6</t>
+          <t>https://www.indeed.com/viewjob?jk=322e0a73c296fcdc</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>IT System Administrator</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t xml:space="preserve">Tailored Edge Connections </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>North Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998975ecfa0fdb90</t>
+          <t>https://www.indeed.com/viewjob?jk=f856c765cc7cbf0f</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior IT Database Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Pegasystems</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Clarks Summit, PA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,67 +986,67 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Databricks Administrator (AWS) New</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Advanced software systems</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
+          <t>https://www.indeed.com/viewjob?jk=1bf73fd986d212e6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Enterprise Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Healthfirst (New York)</t>
+          <t>Empirx Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Kafka, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
+          <t>https://www.indeed.com/viewjob?jk=998975ecfa0fdb90</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
+          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior VR/XR &amp; Computer Vision Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>IVN</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, PostgreSQL, MySQL, NoSQL, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe26087c7f2c3c7</t>
+          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Qorvo</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Clarks Summit, PA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Java Application Developer **REMOTE AVAILABLE**</t>
+          <t>Senior Full- Stack Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vanderbilt University Medical Center</t>
+          <t>Monks</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>EMR, RDS, Azure, Databricks, GCP, Scala, MySQL, MS Excel, CI/CD, Docker</t>
+          <t>Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37699040bc322434</t>
+          <t>https://www.indeed.com/viewjob?jk=8f0ce256017494b0</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
+          <t>Senior Databricks Administrator (AWS) New</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Advanced software systems</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
+          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer II - Identity &amp; Access Management</t>
+          <t>Genesys Cloud GenAI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Fustis LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Kafka, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2429610d97c33cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=4735299b123e3950</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AliCloud Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Vaarida Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
+          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Salt Dental Partners</t>
+          <t>Healthfirst (New York)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Devops Engineer-1</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UI/UX Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>Qorvo</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
+          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior VR/XR &amp; Computer Vision Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>IVN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, Scala, PostgreSQL, MySQL, NoSQL, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe26087c7f2c3c7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Analyst — AI-Driven Insights</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>David's Bridal</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Snowflake, dbt, Tableau, Airflow, Git, Python</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
+          <t>https://www.indeed.com/viewjob?jk=6162c1000e2759f6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Developer – T-SQL, Azure Logic Apps (Remote)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, ETL, Power BI, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
+          <t>https://www.indeed.com/viewjob?jk=c4a0bd8c3f6a6cba</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>Software Engineer II - Identity &amp; Access Management</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Klaviyo</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, API Gateway, IAM, RDS, Kafka, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
+          <t>https://www.indeed.com/viewjob?jk=2429610d97c33cfd</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AliCloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>Vaarida Technologies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,367 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Salt Dental Partners</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Franklin, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-04-05</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Devops Engineer-1</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Irvine, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>UI/UX Engineer</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>NIKSUN, Inc.</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Princeton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Senior Engineer</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ML Engineer</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>NYU Langone Health</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Data Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Trenton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Indeed</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>AWS, Redshift, RDS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-04-06</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=81fc0c21d444af23</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Data Analyst (Sales Ops)- Temp</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Hive, MapReduce, HBase, Scala, Oracle, SQL Server, ETL, Tableau</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=45b583a24b7d9b26</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-06.xlsx
+++ b/results/job_matches_2026-04-06.xlsx
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Intern - Data Engineer - Summer 2026</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>oura</t>
+          <t>Acxiom</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Conway, AR, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>22.2</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Athena, S3, RDS, Azure, Databricks, GCP, BigQuery</t>
+          <t>AWS, S3, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42ae77d7fc82e8f5</t>
+          <t>https://www.indeed.com/viewjob?jk=338baa6df1016586</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Intern - Data Engineer - Summer 2026</t>
+          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Acxiom</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Conway, AR, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=338baa6df1016586</t>
+          <t>https://www.indeed.com/viewjob?jk=c44885cba017a052</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineering Advisor –Evernorth</t>
+          <t>AI Solutions Architect - Founding</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The Cigna Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bloomington, MN, US USA</t>
+          <t>West Palm Beach, FL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Databricks, Unity Catalog, Spark, Scala, Databricks Lakehouse</t>
+          <t>AWS, S3, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6e200e992325ba5</t>
+          <t>https://www.indeed.com/viewjob?jk=dad27261ac45880f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior MLOps Engineer - Analytics &amp; AI</t>
+          <t>Java Backend Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>athenahealth</t>
+          <t>Koya Consulting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Athena, RDS, Azure, GCP, Spark, Scala, Snowflake, MySQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b90e39d495953c19</t>
+          <t>https://www.indeed.com/viewjob?jk=72cf88180937d8f9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OneMagnify</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
+          <t>https://www.indeed.com/viewjob?jk=c95daa9d3325b0e6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Analytics / Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e41b246b13bc8e16</t>
+          <t>https://www.indeed.com/viewjob?jk=b61231aa2a194a10</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior MLOps Engineer - Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>athenahealth</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Athena, RDS, Azure, GCP, Spark, Scala, Snowflake, MySQL, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d05ebd191671b98</t>
+          <t>https://www.indeed.com/viewjob?jk=b90e39d495953c19</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Computer Programmer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>OneMagnify</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
+          <t>https://www.indeed.com/viewjob?jk=c213109ba33f094f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - Full Stack + AWS + Elastic / Open Search</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, ECS, RDS, Spark, Scala, Kafka, PostgreSQL, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, HBase, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ce76eb1050277d8</t>
+          <t>https://www.indeed.com/viewjob?jk=fb06ddb826f8d860</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Healthcare Application Developer (AWS / Clinical AI)</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Careficient</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, SQS, SNS, IAM, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76e0e8781165273c</t>
+          <t>https://www.indeed.com/viewjob?jk=e41b246b13bc8e16</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LLM Operations Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Health Business Solutions</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
+          <t>https://www.indeed.com/viewjob?jk=9d05ebd191671b98</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Computer Programmer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>GAINSCO</t>
+          <t>Axle</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Kafka, Snowflake, SQL Server, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=322e0a73c296fcdc</t>
+          <t>https://www.indeed.com/viewjob?jk=82e8ba86f3bb725f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>IT System Administrator</t>
+          <t>EverHealth – Senior Data Engineer (Remote, US)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tailored Edge Connections </t>
+          <t>Evercommerce</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>North Aurora, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Redshift, RDS, BigQuery, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f856c765cc7cbf0f</t>
+          <t>https://www.indeed.com/viewjob?jk=606cdb554cde0461</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior IT Database Engineer</t>
+          <t>LLM Operations Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Pegasystems</t>
+          <t>Health Business Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
+          <t>Azure, Databricks, Unity Catalog, Delta Live Tables, Spark, PySpark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
+          <t>https://www.indeed.com/viewjob?jk=29f380b4ee93c576</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior IT Database Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Pegasystems</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,42 +1011,42 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Dataflow, Scala, MongoDB, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, HDFS, Spark, Kafka, Snowflake, Oracle, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bf73fd986d212e6</t>
+          <t>https://www.indeed.com/viewjob?jk=ea0b20148ccd5d08</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Enterprise Architect</t>
+          <t>Cloud DevSecOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Empirx Health</t>
+          <t>Regions Financial</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hoover, AL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Kafka, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=998975ecfa0fdb90</t>
+          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud DevSecOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Regions Financial</t>
+          <t>Vizient, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hoover, AL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88befaf12f2cc91c</t>
+          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vizient, Inc.</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Clarks Summit, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, SQL Server, MongoDB, CI/CD, Jenkins, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f24e485db8e99c</t>
+          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Junior Software Engineer</t>
+          <t>Senior Databricks Administrator (AWS) New</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Advanced software systems</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Clarks Summit, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ETL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8fca3b486bed796</t>
+          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Full- Stack Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Monks</t>
+          <t>FireMon</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Scala, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, S3, IAM, RDS, PostgreSQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f0ce256017494b0</t>
+          <t>https://www.indeed.com/viewjob?jk=5a9f14ac4c33a585</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Databricks Administrator (AWS) New</t>
+          <t>Analytics Data Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Advanced software systems</t>
+          <t>Butler Till</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, ETL, ELT, Power BI, Tableau, Git</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a86546443e51144d</t>
+          <t>https://www.indeed.com/viewjob?jk=cb30244a11aaad6a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Genesys Cloud GenAI Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Fustis LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4735299b123e3950</t>
+          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Healthfirst (New York)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22afb06d679561e6</t>
+          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Junior Automation Tester (AI enabled Testing)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Healthfirst (New York)</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bridgewater, NJ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, RDS, Azure, GCP, Hadoop, Spark, PySpark, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, ELT, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7e1ba2fbbe4b720</t>
+          <t>https://www.indeed.com/viewjob?jk=31c5a628a0bbcd11</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AdCellerant</t>
+          <t>Labcorp</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, SQS, API Gateway, ECS, RDS, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
+          <t>https://www.indeed.com/viewjob?jk=df4b1cc4ed807ce6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineering Intern</t>
+          <t>Senior Backend Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Qorvo</t>
+          <t>AdCellerant</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c4e369ba11565e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior VR/XR &amp; Computer Vision Software Engineer</t>
+          <t>Data Engineering Intern</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IVN</t>
+          <t>Qorvo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, PostgreSQL, MySQL, NoSQL, Terraform, AWS CloudFormation, Docker, Kubernetes</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe26087c7f2c3c7</t>
+          <t>https://www.indeed.com/viewjob?jk=4d4176ecd7b00cdf</t>
         </is>
       </c>
     </row>
@@ -1518,25 +1518,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer II - Identity &amp; Access Management</t>
+          <t>AliCloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Klaviyo</t>
+          <t>Vaarida Technologies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Kafka, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2429610d97c33cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AliCloud Engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Vaarida Technologies</t>
+          <t>Salt Dental Partners</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Franklin, TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kafka, PostgreSQL, DynamoDB, Cassandra, ETL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-05</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=875f29ca149584b4</t>
+          <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Junior Automation Tester (AI enabled Testing)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Salt Dental Partners</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Franklin, TN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-05</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21381131f52aaafb</t>
+          <t>https://www.indeed.com/viewjob?jk=f99abb391ef4c38f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Devops Engineer-1</t>
+          <t>Junior Automation Tester (AI enabled Testing)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
+          <t>https://www.indeed.com/viewjob?jk=85aec2fe5dbdec6e</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>UI/UX Engineer</t>
+          <t>Devops Engineer-1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NIKSUN, Inc.</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
+          <t>AWS, S3, IAM, Azure, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
+          <t>https://www.indeed.com/viewjob?jk=d21b43139fbc9c58</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>UI/UX Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NIKSUN, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
+          <t>https://www.indeed.com/viewjob?jk=3368fc7b71b947f0</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ce918c4d6c656402</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
+          <t>https://www.indeed.com/viewjob?jk=bc707a9bbacf36ab</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ML Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
+          <t>https://www.indeed.com/viewjob?jk=a0d95f3260031a05</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Operations Engineer</t>
+          <t>ML Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Trenton, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, ETL, ELT, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
+          <t>https://www.indeed.com/viewjob?jk=72534c2968374dee</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Operations Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Trenton, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, RDS, Spark, Scala, Snowflake, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81fc0c21d444af23</t>
+          <t>https://www.indeed.com/viewjob?jk=5c98f422ee056842</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Analyst (Sales Ops)- Temp</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hive, MapReduce, HBase, Scala, Oracle, SQL Server, ETL, Tableau</t>
+          <t>AWS, Redshift, RDS, Hive, Spark, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b583a24b7d9b26</t>
+          <t>https://www.indeed.com/viewjob?jk=81fc0c21d444af23</t>
         </is>
       </c>
     </row>
